--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/115.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/115.xlsx
@@ -426,13 +426,13 @@
         <v>-7.690287570952108</v>
       </c>
       <c r="E2">
-        <v>-10.2419611703755</v>
+        <v>-8.909607133260746</v>
       </c>
       <c r="F2">
-        <v>-7.16428315332191</v>
+        <v>-6.819520273692714</v>
       </c>
       <c r="G2">
-        <v>-8.225097890625149</v>
+        <v>-9.026435301678974</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.773708480367867</v>
       </c>
       <c r="E3">
-        <v>-10.50675463102601</v>
+        <v>-9.794516239099611</v>
       </c>
       <c r="F3">
-        <v>-7.190891788260166</v>
+        <v>-6.788672849871785</v>
       </c>
       <c r="G3">
-        <v>-8.040925621184414</v>
+        <v>-8.113992671781668</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.900076828991608</v>
       </c>
       <c r="E4">
-        <v>-11.11737859469428</v>
+        <v>-11.5502010833994</v>
       </c>
       <c r="F4">
-        <v>-7.013091500692653</v>
+        <v>-6.59380496365358</v>
       </c>
       <c r="G4">
-        <v>-8.058786014368781</v>
+        <v>-8.127734746315182</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.013168726065615</v>
       </c>
       <c r="E5">
-        <v>-11.95594329753865</v>
+        <v>-11.74829012191693</v>
       </c>
       <c r="F5">
-        <v>-7.092671535164048</v>
+        <v>-6.752751628224265</v>
       </c>
       <c r="G5">
-        <v>-7.774052613627145</v>
+        <v>-8.234827583965066</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.071367765743959</v>
       </c>
       <c r="E6">
-        <v>-12.16567051425589</v>
+        <v>-11.35132409040454</v>
       </c>
       <c r="F6">
-        <v>-6.681619081105824</v>
+        <v>-6.523344699696242</v>
       </c>
       <c r="G6">
-        <v>-7.928390246667968</v>
+        <v>-8.634076065455632</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.034668405549684</v>
       </c>
       <c r="E7">
-        <v>-13.40528593216755</v>
+        <v>-13.13842748736955</v>
       </c>
       <c r="F7">
-        <v>-6.81843107994937</v>
+        <v>-6.711507966921434</v>
       </c>
       <c r="G7">
-        <v>-8.601510228985822</v>
+        <v>-8.296191856080997</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.884913660457851</v>
       </c>
       <c r="E8">
-        <v>-13.97593705577013</v>
+        <v>-14.2957333617178</v>
       </c>
       <c r="F8">
-        <v>-6.693853605229073</v>
+        <v>-6.837699633896043</v>
       </c>
       <c r="G8">
-        <v>-8.189340688255481</v>
+        <v>-7.917465446388372</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.622274363657124</v>
       </c>
       <c r="E9">
-        <v>-14.37540280493475</v>
+        <v>-14.79556368031442</v>
       </c>
       <c r="F9">
-        <v>-6.792020804177024</v>
+        <v>-6.460264901231332</v>
       </c>
       <c r="G9">
-        <v>-7.961790340613675</v>
+        <v>-8.420976249092746</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.260967099541688</v>
       </c>
       <c r="E10">
-        <v>-15.65825609267165</v>
+        <v>-16.23178279726909</v>
       </c>
       <c r="F10">
-        <v>-7.120414103537759</v>
+        <v>-6.426615109793032</v>
       </c>
       <c r="G10">
-        <v>-7.338338473021507</v>
+        <v>-7.39832886873864</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.827347760122707</v>
       </c>
       <c r="E11">
-        <v>-16.88981082684966</v>
+        <v>-16.37014126362545</v>
       </c>
       <c r="F11">
-        <v>-6.833099364138171</v>
+        <v>-6.833885674125186</v>
       </c>
       <c r="G11">
-        <v>-7.130585187704543</v>
+        <v>-8.085015466676428</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.352809090598944</v>
       </c>
       <c r="E12">
-        <v>-16.61274520163837</v>
+        <v>-16.92192223603806</v>
       </c>
       <c r="F12">
-        <v>-7.1811147797912</v>
+        <v>-7.031106155480776</v>
       </c>
       <c r="G12">
-        <v>-7.37657196345455</v>
+        <v>-8.03085163110841</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.870197238610045</v>
       </c>
       <c r="E13">
-        <v>-17.29815238506932</v>
+        <v>-17.32899129306155</v>
       </c>
       <c r="F13">
-        <v>-7.02038129902142</v>
+        <v>-6.453695689094088</v>
       </c>
       <c r="G13">
-        <v>-6.542400561742232</v>
+        <v>-7.025170796643071</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.417967674567491</v>
       </c>
       <c r="E14">
-        <v>-18.36285549443472</v>
+        <v>-18.65484244150129</v>
       </c>
       <c r="F14">
-        <v>-7.215402804713422</v>
+        <v>-6.377066494669635</v>
       </c>
       <c r="G14">
-        <v>-6.144876874477626</v>
+        <v>-6.626832715175804</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.029182659993897</v>
       </c>
       <c r="E15">
-        <v>-19.13272777505673</v>
+        <v>-18.77978303937291</v>
       </c>
       <c r="F15">
-        <v>-7.039788823162173</v>
+        <v>-6.752714807061731</v>
       </c>
       <c r="G15">
-        <v>-4.875103890708005</v>
+        <v>-5.908990573167936</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.73682831315873</v>
       </c>
       <c r="E16">
-        <v>-20.26050799887497</v>
+        <v>-19.35707290587073</v>
       </c>
       <c r="F16">
-        <v>-6.635931936930748</v>
+        <v>-6.294250949012997</v>
       </c>
       <c r="G16">
-        <v>-4.695953718850345</v>
+        <v>-5.666085915314992</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.568503526315956</v>
       </c>
       <c r="E17">
-        <v>-20.99902965394189</v>
+        <v>-20.94794846713537</v>
       </c>
       <c r="F17">
-        <v>-6.610199091363731</v>
+        <v>-6.455044214681085</v>
       </c>
       <c r="G17">
-        <v>-4.069499186454059</v>
+        <v>-4.867784274520677</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.540108556817859</v>
       </c>
       <c r="E18">
-        <v>-21.78614636358511</v>
+        <v>-21.86456141950193</v>
       </c>
       <c r="F18">
-        <v>-6.333121822928022</v>
+        <v>-5.643827284733283</v>
       </c>
       <c r="G18">
-        <v>-3.636390445187827</v>
+        <v>-3.921322478661819</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.658488467809521</v>
       </c>
       <c r="E19">
-        <v>-23.03089254254747</v>
+        <v>-22.78221139241625</v>
       </c>
       <c r="F19">
-        <v>-6.147707869172033</v>
+        <v>-5.53552080458821</v>
       </c>
       <c r="G19">
-        <v>-3.136948302951219</v>
+        <v>-3.819337812779031</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.91498820130094</v>
       </c>
       <c r="E20">
-        <v>-22.95951020676456</v>
+        <v>-22.94971058901196</v>
       </c>
       <c r="F20">
-        <v>-5.940720673435928</v>
+        <v>-4.960296644217787</v>
       </c>
       <c r="G20">
-        <v>-2.744499681998315</v>
+        <v>-3.410405985586097</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.289301269546224</v>
       </c>
       <c r="E21">
-        <v>-23.40644342047758</v>
+        <v>-24.03345140310561</v>
       </c>
       <c r="F21">
-        <v>-5.538865591481619</v>
+        <v>-5.107871112536181</v>
       </c>
       <c r="G21">
-        <v>-3.280940481181819</v>
+        <v>-3.598699884223224</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.753409081928314</v>
       </c>
       <c r="E22">
-        <v>-24.59767209361729</v>
+        <v>-24.82636908795266</v>
       </c>
       <c r="F22">
-        <v>-5.038052645401075</v>
+        <v>-4.532584395782098</v>
       </c>
       <c r="G22">
-        <v>-2.576976146074576</v>
+        <v>-3.179190864032319</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.267420396268746</v>
       </c>
       <c r="E23">
-        <v>-25.51777649944377</v>
+        <v>-25.31719227174802</v>
       </c>
       <c r="F23">
-        <v>-4.770060305949285</v>
+        <v>-4.310601880585654</v>
       </c>
       <c r="G23">
-        <v>-3.019999971230924</v>
+        <v>-3.703356160356204</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.794357133266053</v>
       </c>
       <c r="E24">
-        <v>-25.33461783972953</v>
+        <v>-26.01454104113719</v>
       </c>
       <c r="F24">
-        <v>-4.480756827846384</v>
+        <v>-4.160414297506786</v>
       </c>
       <c r="G24">
-        <v>-2.971510410717219</v>
+        <v>-3.9958163743865</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.298082433125159</v>
       </c>
       <c r="E25">
-        <v>-25.7595019134992</v>
+        <v>-25.85978044192506</v>
       </c>
       <c r="F25">
-        <v>-4.379752815677403</v>
+        <v>-3.654812224737953</v>
       </c>
       <c r="G25">
-        <v>-4.226028400641878</v>
+        <v>-3.65236382741481</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.744463682775906</v>
       </c>
       <c r="E26">
-        <v>-26.0034462798184</v>
+        <v>-26.39125120841326</v>
       </c>
       <c r="F26">
-        <v>-4.445939053295448</v>
+        <v>-3.722582960124396</v>
       </c>
       <c r="G26">
-        <v>-4.364955444197394</v>
+        <v>-4.520074365985485</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.10964592207733</v>
       </c>
       <c r="E27">
-        <v>-26.14289157993659</v>
+        <v>-25.88456930864304</v>
       </c>
       <c r="F27">
-        <v>-4.268798379241715</v>
+        <v>-3.666770788105437</v>
       </c>
       <c r="G27">
-        <v>-4.505349059426806</v>
+        <v>-5.252012810899569</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.376486962896015</v>
       </c>
       <c r="E28">
-        <v>-25.96962310745511</v>
+        <v>-26.72821043085001</v>
       </c>
       <c r="F28">
-        <v>-4.434336823758938</v>
+        <v>-3.454966750827523</v>
       </c>
       <c r="G28">
-        <v>-4.848069975834317</v>
+        <v>-5.280291490896023</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.538281326392502</v>
       </c>
       <c r="E29">
-        <v>-26.51649974251741</v>
+        <v>-26.78420048348084</v>
       </c>
       <c r="F29">
-        <v>-4.22801399265436</v>
+        <v>-3.51614451848799</v>
       </c>
       <c r="G29">
-        <v>-5.186967212143969</v>
+        <v>-5.199457900463639</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.598312661269034</v>
       </c>
       <c r="E30">
-        <v>-24.91864580280696</v>
+        <v>-25.43795308811056</v>
       </c>
       <c r="F30">
-        <v>-3.705643641652856</v>
+        <v>-3.93363315338656</v>
       </c>
       <c r="G30">
-        <v>-4.842130857136865</v>
+        <v>-4.923361713033962</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.564437756534142</v>
       </c>
       <c r="E31">
-        <v>-26.0382838303594</v>
+        <v>-25.5768368574518</v>
       </c>
       <c r="F31">
-        <v>-4.112492148358545</v>
+        <v>-3.480918939663828</v>
       </c>
       <c r="G31">
-        <v>-4.763876181679572</v>
+        <v>-5.318217100593914</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.449099525127037</v>
       </c>
       <c r="E32">
-        <v>-25.19334303611224</v>
+        <v>-24.83018206306712</v>
       </c>
       <c r="F32">
-        <v>-4.023762648887177</v>
+        <v>-3.535989937314362</v>
       </c>
       <c r="G32">
-        <v>-4.68166540430285</v>
+        <v>-5.989943343239735</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.267620884042746</v>
       </c>
       <c r="E33">
-        <v>-25.40811497287402</v>
+        <v>-23.59565664994007</v>
       </c>
       <c r="F33">
-        <v>-4.155949830531162</v>
+        <v>-3.877668945599719</v>
       </c>
       <c r="G33">
-        <v>-4.91278783058153</v>
+        <v>-5.364720333784057</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.033344432536468</v>
       </c>
       <c r="E34">
-        <v>-24.58318550526675</v>
+        <v>-25.84530743899654</v>
       </c>
       <c r="F34">
-        <v>-4.320641784236583</v>
+        <v>-4.159829910023988</v>
       </c>
       <c r="G34">
-        <v>-4.458673677868622</v>
+        <v>-5.776436329775518</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.759060697374442</v>
       </c>
       <c r="E35">
-        <v>-23.54881411480473</v>
+        <v>-24.35000532166379</v>
       </c>
       <c r="F35">
-        <v>-4.589616813208903</v>
+        <v>-3.851958271915517</v>
       </c>
       <c r="G35">
-        <v>-4.426101220307733</v>
+        <v>-5.558450148196667</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.456735670941736</v>
       </c>
       <c r="E36">
-        <v>-23.35641736811484</v>
+        <v>-23.94496502099573</v>
       </c>
       <c r="F36">
-        <v>-4.543633120101161</v>
+        <v>-3.821270802392047</v>
       </c>
       <c r="G36">
-        <v>-4.126642513007418</v>
+        <v>-4.653644946858459</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.133001569499765</v>
       </c>
       <c r="E37">
-        <v>-23.47981375634985</v>
+        <v>-23.23804305755434</v>
       </c>
       <c r="F37">
-        <v>-4.752594405260862</v>
+        <v>-4.307193745455629</v>
       </c>
       <c r="G37">
-        <v>-3.450738361891038</v>
+        <v>-5.123782139981439</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.794501677287371</v>
       </c>
       <c r="E38">
-        <v>-22.80937770798826</v>
+        <v>-23.00805544812679</v>
       </c>
       <c r="F38">
-        <v>-4.988884119697384</v>
+        <v>-4.475799036478101</v>
       </c>
       <c r="G38">
-        <v>-3.011591185561176</v>
+        <v>-3.578200986244057</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.450610313634503</v>
       </c>
       <c r="E39">
-        <v>-22.29372037273484</v>
+        <v>-22.77346238063343</v>
       </c>
       <c r="F39">
-        <v>-4.929556912399107</v>
+        <v>-4.253845819841093</v>
       </c>
       <c r="G39">
-        <v>-3.741437365694441</v>
+        <v>-3.347638042161516</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.107996817550356</v>
       </c>
       <c r="E40">
-        <v>-22.12150703469715</v>
+        <v>-22.3312433083624</v>
       </c>
       <c r="F40">
-        <v>-4.874921433875319</v>
+        <v>-4.221636408932886</v>
       </c>
       <c r="G40">
-        <v>-2.887415932928653</v>
+        <v>-3.896721814759495</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.775487006540733</v>
       </c>
       <c r="E41">
-        <v>-22.06264592954545</v>
+        <v>-21.88133488722634</v>
       </c>
       <c r="F41">
-        <v>-5.092705544689933</v>
+        <v>-4.43401691516402</v>
       </c>
       <c r="G41">
-        <v>-2.973139199122541</v>
+        <v>-2.871088322328967</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.459412642790864</v>
       </c>
       <c r="E42">
-        <v>-20.77689894691764</v>
+        <v>-20.97220297392045</v>
       </c>
       <c r="F42">
-        <v>-5.031774043299316</v>
+        <v>-4.541109484724909</v>
       </c>
       <c r="G42">
-        <v>-3.228630551115795</v>
+        <v>-4.062917821921987</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.161005774105421</v>
       </c>
       <c r="E43">
-        <v>-20.92938625217792</v>
+        <v>-21.04887456734431</v>
       </c>
       <c r="F43">
-        <v>-5.188332875275997</v>
+        <v>-4.216159162024338</v>
       </c>
       <c r="G43">
-        <v>-2.439108477091627</v>
+        <v>-3.406880254586773</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.887057921933503</v>
       </c>
       <c r="E44">
-        <v>-20.01032339537321</v>
+        <v>-20.55668831287264</v>
       </c>
       <c r="F44">
-        <v>-4.984346010396693</v>
+        <v>-4.365910434123504</v>
       </c>
       <c r="G44">
-        <v>-1.810482226821579</v>
+        <v>-4.145539106945578</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.639271871093118</v>
       </c>
       <c r="E45">
-        <v>-19.75766624506326</v>
+        <v>-18.91701391570135</v>
       </c>
       <c r="F45">
-        <v>-5.068814549102571</v>
+        <v>-4.376609159435255</v>
       </c>
       <c r="G45">
-        <v>-2.288382649234149</v>
+        <v>-3.707279156820241</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.418093133288974</v>
       </c>
       <c r="E46">
-        <v>-19.049050632343</v>
+        <v>-19.55157539297418</v>
       </c>
       <c r="F46">
-        <v>-4.993731843504545</v>
+        <v>-4.312577553715165</v>
       </c>
       <c r="G46">
-        <v>-2.378581772997132</v>
+        <v>-2.161135210341182</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.225960226644505</v>
       </c>
       <c r="E47">
-        <v>-18.89098877557927</v>
+        <v>-18.37241963153892</v>
       </c>
       <c r="F47">
-        <v>-4.866663199379261</v>
+        <v>-4.416393435737009</v>
       </c>
       <c r="G47">
-        <v>-2.486492315395215</v>
+        <v>-2.373539812140822</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.060489765680233</v>
       </c>
       <c r="E48">
-        <v>-16.71583591242299</v>
+        <v>-18.24274677832928</v>
       </c>
       <c r="F48">
-        <v>-5.362636340182221</v>
+        <v>-4.702253145326788</v>
       </c>
       <c r="G48">
-        <v>-1.363876391391738</v>
+        <v>-2.664109704668193</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.920403740269752</v>
       </c>
       <c r="E49">
-        <v>-17.80533241698038</v>
+        <v>-16.90569671366857</v>
       </c>
       <c r="F49">
-        <v>-5.197390089406396</v>
+        <v>-4.785315353179755</v>
       </c>
       <c r="G49">
-        <v>-1.604125991722188</v>
+        <v>-2.879629529820287</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.805054027420543</v>
       </c>
       <c r="E50">
-        <v>-17.20547716450234</v>
+        <v>-17.07921878069449</v>
       </c>
       <c r="F50">
-        <v>-5.406364836066377</v>
+        <v>-4.93484490645076</v>
       </c>
       <c r="G50">
-        <v>-2.451307837403841</v>
+        <v>-2.688703747479439</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.712106205404648</v>
       </c>
       <c r="E51">
-        <v>-16.08102989755375</v>
+        <v>-17.19971241709058</v>
       </c>
       <c r="F51">
-        <v>-5.169572295001702</v>
+        <v>-4.717380704231065</v>
       </c>
       <c r="G51">
-        <v>-1.572579803278472</v>
+        <v>-3.010700648811112</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.642522956646213</v>
       </c>
       <c r="E52">
-        <v>-15.89923430851582</v>
+        <v>-16.69639970198206</v>
       </c>
       <c r="F52">
-        <v>-5.091143218804352</v>
+        <v>-4.851204645938656</v>
       </c>
       <c r="G52">
-        <v>-2.104309696159593</v>
+        <v>-2.574940160567924</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.595690168719323</v>
       </c>
       <c r="E53">
-        <v>-14.20763189989857</v>
+        <v>-16.82414795373845</v>
       </c>
       <c r="F53">
-        <v>-5.401789509676672</v>
+        <v>-4.836720863489004</v>
       </c>
       <c r="G53">
-        <v>-1.370077043186793</v>
+        <v>-2.746598567870214</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.572707388348286</v>
       </c>
       <c r="E54">
-        <v>-14.9508858103035</v>
+        <v>-15.45473741381893</v>
       </c>
       <c r="F54">
-        <v>-5.208978065589666</v>
+        <v>-5.06781127140514</v>
       </c>
       <c r="G54">
-        <v>-2.335395706437339</v>
+        <v>-3.724301981983173</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.577150792687029</v>
       </c>
       <c r="E55">
-        <v>-14.55022454400086</v>
+        <v>-15.78679229890536</v>
       </c>
       <c r="F55">
-        <v>-5.643742556466807</v>
+        <v>-5.204306924992077</v>
       </c>
       <c r="G55">
-        <v>-2.299615330248896</v>
+        <v>-2.509033819972113</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.609607772739944</v>
       </c>
       <c r="E56">
-        <v>-14.1206218003152</v>
+        <v>-13.39169145319653</v>
       </c>
       <c r="F56">
-        <v>-5.273836365797615</v>
+        <v>-4.891513128898421</v>
       </c>
       <c r="G56">
-        <v>-2.045653450294786</v>
+        <v>-3.585120026421134</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.67189696520577</v>
       </c>
       <c r="E57">
-        <v>-13.92423093955055</v>
+        <v>-13.90756615520232</v>
       </c>
       <c r="F57">
-        <v>-5.186384125147049</v>
+        <v>-5.128384855258868</v>
       </c>
       <c r="G57">
-        <v>-2.798392052832111</v>
+        <v>-2.964369563989012</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.764065456785309</v>
       </c>
       <c r="E58">
-        <v>-13.71847972301205</v>
+        <v>-13.99329922511554</v>
       </c>
       <c r="F58">
-        <v>-5.681442675783844</v>
+        <v>-4.784516373545417</v>
       </c>
       <c r="G58">
-        <v>-2.602599768548535</v>
+        <v>-3.527850899137282</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.883946997461538</v>
       </c>
       <c r="E59">
-        <v>-13.11612928135578</v>
+        <v>-12.78148410913696</v>
       </c>
       <c r="F59">
-        <v>-5.420166041266475</v>
+        <v>-4.987084237924488</v>
       </c>
       <c r="G59">
-        <v>-3.164429141472708</v>
+        <v>-3.211961954325564</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.028373897913071</v>
       </c>
       <c r="E60">
-        <v>-12.88173999519277</v>
+        <v>-12.6372793828367</v>
       </c>
       <c r="F60">
-        <v>-5.913045412563624</v>
+        <v>-5.136306552247897</v>
       </c>
       <c r="G60">
-        <v>-3.042031651794774</v>
+        <v>-3.28997495995849</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.190501653729899</v>
       </c>
       <c r="E61">
-        <v>-12.2890080323288</v>
+        <v>-12.66563215859873</v>
       </c>
       <c r="F61">
-        <v>-5.760971635739466</v>
+        <v>-5.31523206286833</v>
       </c>
       <c r="G61">
-        <v>-2.837069156367416</v>
+        <v>-3.870118270805912</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.363688690326392</v>
       </c>
       <c r="E62">
-        <v>-11.85118610831921</v>
+        <v>-12.58200935757308</v>
       </c>
       <c r="F62">
-        <v>-5.443470273812165</v>
+        <v>-5.041406142677018</v>
       </c>
       <c r="G62">
-        <v>-3.307928048417958</v>
+        <v>-4.610491985754059</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.541567633442701</v>
       </c>
       <c r="E63">
-        <v>-12.41619928178223</v>
+        <v>-12.00927966440099</v>
       </c>
       <c r="F63">
-        <v>-5.342010946192495</v>
+        <v>-5.502001668887934</v>
       </c>
       <c r="G63">
-        <v>-3.407111992774522</v>
+        <v>-4.649228679109072</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.714563249448358</v>
       </c>
       <c r="E64">
-        <v>-11.44217886442043</v>
+        <v>-11.70047849334394</v>
       </c>
       <c r="F64">
-        <v>-5.622082210661342</v>
+        <v>-5.325330563638129</v>
       </c>
       <c r="G64">
-        <v>-3.7174590843535</v>
+        <v>-3.660991109090151</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.874926049540711</v>
       </c>
       <c r="E65">
-        <v>-11.32020894549784</v>
+        <v>-11.3734954991461</v>
       </c>
       <c r="F65">
-        <v>-5.578347379953524</v>
+        <v>-5.251281226149927</v>
       </c>
       <c r="G65">
-        <v>-3.639796996547737</v>
+        <v>-4.042296433757867</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.013461227756413</v>
       </c>
       <c r="E66">
-        <v>-11.49276191908611</v>
+        <v>-10.11012370659019</v>
       </c>
       <c r="F66">
-        <v>-5.701706192971892</v>
+        <v>-5.457491614134509</v>
       </c>
       <c r="G66">
-        <v>-3.665430550658314</v>
+        <v>-4.019870798274844</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.119443008966625</v>
       </c>
       <c r="E67">
-        <v>-11.86279711567488</v>
+        <v>-10.66774188199869</v>
       </c>
       <c r="F67">
-        <v>-5.716677756843498</v>
+        <v>-5.469223707556084</v>
       </c>
       <c r="G67">
-        <v>-4.283095584647835</v>
+        <v>-4.570258925815296</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.184301571530618</v>
       </c>
       <c r="E68">
-        <v>-10.40751312314791</v>
+        <v>-11.15538607704066</v>
       </c>
       <c r="F68">
-        <v>-5.644521739777203</v>
+        <v>-5.771536537901363</v>
       </c>
       <c r="G68">
-        <v>-4.116942614577354</v>
+        <v>-4.327801191610154</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.20219770545327</v>
       </c>
       <c r="E69">
-        <v>-10.43792182610941</v>
+        <v>-10.54719843238851</v>
       </c>
       <c r="F69">
-        <v>-5.939944657537363</v>
+        <v>-5.69329592270795</v>
       </c>
       <c r="G69">
-        <v>-3.861782317138027</v>
+        <v>-5.49861865866542</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.17135398755245</v>
       </c>
       <c r="E70">
-        <v>-10.91544941021825</v>
+        <v>-10.9119941845504</v>
       </c>
       <c r="F70">
-        <v>-6.067560472056431</v>
+        <v>-5.650322854545458</v>
       </c>
       <c r="G70">
-        <v>-4.251493116929953</v>
+        <v>-5.350448571964259</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.094039236558149</v>
       </c>
       <c r="E71">
-        <v>-10.90989750108485</v>
+        <v>-10.34068643221672</v>
       </c>
       <c r="F71">
-        <v>-6.176505185685426</v>
+        <v>-5.686641190451273</v>
       </c>
       <c r="G71">
-        <v>-4.055058586811757</v>
+        <v>-4.083039317709678</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.974364751391971</v>
       </c>
       <c r="E72">
-        <v>-11.2583726329231</v>
+        <v>-11.18732087574275</v>
       </c>
       <c r="F72">
-        <v>-6.288677491970087</v>
+        <v>-5.752085461847935</v>
       </c>
       <c r="G72">
-        <v>-4.087581386189558</v>
+        <v>-4.54862120017062</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.816683258830277</v>
       </c>
       <c r="E73">
-        <v>-10.7685275995134</v>
+        <v>-11.49638016981824</v>
       </c>
       <c r="F73">
-        <v>-6.318451955033306</v>
+        <v>-5.592481163395863</v>
       </c>
       <c r="G73">
-        <v>-4.079129563427799</v>
+        <v>-4.655104897441278</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.627892478414307</v>
       </c>
       <c r="E74">
-        <v>-11.13862619473827</v>
+        <v>-11.04038547961587</v>
       </c>
       <c r="F74">
-        <v>-6.252864754177776</v>
+        <v>-5.884739836736975</v>
       </c>
       <c r="G74">
-        <v>-3.246616745030655</v>
+        <v>-4.063702421214795</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.412410309794838</v>
       </c>
       <c r="E75">
-        <v>-11.19965643893965</v>
+        <v>-10.72307530589841</v>
       </c>
       <c r="F75">
-        <v>-6.333512998289136</v>
+        <v>-6.059341830208258</v>
       </c>
       <c r="G75">
-        <v>-3.608876501210944</v>
+        <v>-4.368249437008969</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.171737769334801</v>
       </c>
       <c r="E76">
-        <v>-11.29948664843874</v>
+        <v>-11.73720441754615</v>
       </c>
       <c r="F76">
-        <v>-6.256303771573152</v>
+        <v>-6.240189167957078</v>
       </c>
       <c r="G76">
-        <v>-4.480586178793058</v>
+        <v>-4.59304872130764</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.908862064270159</v>
       </c>
       <c r="E77">
-        <v>-11.60101961871348</v>
+        <v>-12.71468458904981</v>
       </c>
       <c r="F77">
-        <v>-6.19303353247191</v>
+        <v>-6.378664453938314</v>
       </c>
       <c r="G77">
-        <v>-3.748336542598282</v>
+        <v>-4.095351236570227</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.623098867637753</v>
       </c>
       <c r="E78">
-        <v>-12.53934207547281</v>
+        <v>-12.18551881583151</v>
       </c>
       <c r="F78">
-        <v>-6.396800262228969</v>
+        <v>-6.537518867639426</v>
       </c>
       <c r="G78">
-        <v>-3.189264854108321</v>
+        <v>-4.058614112720934</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.313541044163841</v>
       </c>
       <c r="E79">
-        <v>-13.41179787779059</v>
+        <v>-13.25183859041764</v>
       </c>
       <c r="F79">
-        <v>-6.766609054984361</v>
+        <v>-6.508224663395063</v>
       </c>
       <c r="G79">
-        <v>-3.633808219667195</v>
+        <v>-4.126523333368005</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.982730738005284</v>
       </c>
       <c r="E80">
-        <v>-13.42326397397801</v>
+        <v>-14.28038636330581</v>
       </c>
       <c r="F80">
-        <v>-6.840303642347505</v>
+        <v>-6.273537263418485</v>
       </c>
       <c r="G80">
-        <v>-3.507070604787276</v>
+        <v>-3.266043026255098</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.630844855932108</v>
       </c>
       <c r="E81">
-        <v>-14.50470432327576</v>
+        <v>-14.7297241967169</v>
       </c>
       <c r="F81">
-        <v>-6.709948808447684</v>
+        <v>-6.577362928839488</v>
       </c>
       <c r="G81">
-        <v>-2.99422075311662</v>
+        <v>-3.260603799934076</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.262057404911295</v>
       </c>
       <c r="E82">
-        <v>-15.35920019767911</v>
+        <v>-14.84296774622671</v>
       </c>
       <c r="F82">
-        <v>-6.82100460206196</v>
+        <v>-6.20177400541922</v>
       </c>
       <c r="G82">
-        <v>-2.801159668902942</v>
+        <v>-3.231050559905002</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.88357405344645</v>
       </c>
       <c r="E83">
-        <v>-17.27140721758002</v>
+        <v>-15.7876979937069</v>
       </c>
       <c r="F83">
-        <v>-6.903545374742269</v>
+        <v>-6.688530373720802</v>
       </c>
       <c r="G83">
-        <v>-2.979369645827449</v>
+        <v>-3.150845973125079</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.505392942314094</v>
       </c>
       <c r="E84">
-        <v>-16.70103685936592</v>
+        <v>-16.28718867675294</v>
       </c>
       <c r="F84">
-        <v>-6.85429291262506</v>
+        <v>-6.763238136943348</v>
       </c>
       <c r="G84">
-        <v>-3.124149733896396</v>
+        <v>-2.431414769258361</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.147920069520849</v>
       </c>
       <c r="E85">
-        <v>-18.31813228513496</v>
+        <v>-17.73354704701079</v>
       </c>
       <c r="F85">
-        <v>-7.254319210173516</v>
+        <v>-6.677961908220595</v>
       </c>
       <c r="G85">
-        <v>-2.646110268571176</v>
+        <v>-2.536762949409049</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8310023553672188</v>
       </c>
       <c r="E86">
-        <v>-18.95030272813174</v>
+        <v>-18.96368436882441</v>
       </c>
       <c r="F86">
-        <v>-7.187530372454646</v>
+        <v>-6.776184140949108</v>
       </c>
       <c r="G86">
-        <v>-2.505610715884507</v>
+        <v>-3.043471739104357</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.5747508336955292</v>
       </c>
       <c r="E87">
-        <v>-20.92235806051802</v>
+        <v>-20.44881553353593</v>
       </c>
       <c r="F87">
-        <v>-7.367266740503784</v>
+        <v>-6.604130330295766</v>
       </c>
       <c r="G87">
-        <v>-2.181885709781334</v>
+        <v>-3.03800933896456</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3982589607361596</v>
       </c>
       <c r="E88">
-        <v>-22.79026301920189</v>
+        <v>-22.41311358994707</v>
       </c>
       <c r="F88">
-        <v>-7.381507424095416</v>
+        <v>-6.984047126056451</v>
       </c>
       <c r="G88">
-        <v>-2.767349067310365</v>
+        <v>-2.701141467070481</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.3157920834385799</v>
       </c>
       <c r="E89">
-        <v>-23.5722353823724</v>
+        <v>-22.38383247701347</v>
       </c>
       <c r="F89">
-        <v>-7.283354478500704</v>
+        <v>-7.327984498977224</v>
       </c>
       <c r="G89">
-        <v>-2.510702334923906</v>
+        <v>-3.489888873438459</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.3398537672971101</v>
       </c>
       <c r="E90">
-        <v>-25.20727715063384</v>
+        <v>-24.6530553307311</v>
       </c>
       <c r="F90">
-        <v>-7.039983223063293</v>
+        <v>-7.002177391376401</v>
       </c>
       <c r="G90">
-        <v>-3.014368733268624</v>
+        <v>-2.449592974814499</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.4761558193602531</v>
       </c>
       <c r="E91">
-        <v>-27.3079094455199</v>
+        <v>-27.17442814566981</v>
       </c>
       <c r="F91">
-        <v>-7.161474450880879</v>
+        <v>-7.339193177593747</v>
       </c>
       <c r="G91">
-        <v>-3.530489403932081</v>
+        <v>-2.977757410149824</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.7302295109211731</v>
       </c>
       <c r="E92">
-        <v>-29.28477401730233</v>
+        <v>-28.95347991584918</v>
       </c>
       <c r="F92">
-        <v>-7.345179981880587</v>
+        <v>-7.353148002267641</v>
       </c>
       <c r="G92">
-        <v>-3.752047664147805</v>
+        <v>-3.332992188695779</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.105213777988511</v>
       </c>
       <c r="E93">
-        <v>-31.37489119554258</v>
+        <v>-31.04184683888547</v>
       </c>
       <c r="F93">
-        <v>-7.045992991085907</v>
+        <v>-7.41308929153463</v>
       </c>
       <c r="G93">
-        <v>-3.672121163193181</v>
+        <v>-4.199600315601876</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.596586054268681</v>
       </c>
       <c r="E94">
-        <v>-33.07941107626671</v>
+        <v>-32.73426890129811</v>
       </c>
       <c r="F94">
-        <v>-7.382169017241591</v>
+        <v>-7.035910327375261</v>
       </c>
       <c r="G94">
-        <v>-4.153186467141294</v>
+        <v>-3.303707102855387</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.201666814901076</v>
       </c>
       <c r="E95">
-        <v>-34.69967416960412</v>
+        <v>-34.9542944133964</v>
       </c>
       <c r="F95">
-        <v>-7.06803263445812</v>
+        <v>-6.976149580582633</v>
       </c>
       <c r="G95">
-        <v>-4.209935838775482</v>
+        <v>-4.027531400652718</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.91738034036223</v>
       </c>
       <c r="E96">
-        <v>-38.05851353244034</v>
+        <v>-37.35099154619294</v>
       </c>
       <c r="F96">
-        <v>-6.412158646270422</v>
+        <v>-6.739716540760763</v>
       </c>
       <c r="G96">
-        <v>-4.155080099189758</v>
+        <v>-4.809723926852938</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.719391411156885</v>
       </c>
       <c r="E97">
-        <v>-40.29166482644987</v>
+        <v>-39.1272650975686</v>
       </c>
       <c r="F97">
-        <v>-6.977106138955558</v>
+        <v>-7.015247320370045</v>
       </c>
       <c r="G97">
-        <v>-5.227239998629203</v>
+        <v>-5.157212028837</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.61235394600701</v>
       </c>
       <c r="E98">
-        <v>-43.161016905323</v>
+        <v>-40.44739678333665</v>
       </c>
       <c r="F98">
-        <v>-6.216583635360974</v>
+        <v>-6.959135432006589</v>
       </c>
       <c r="G98">
-        <v>-4.993028833362384</v>
+        <v>-4.699492692031826</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.540334534964442</v>
       </c>
       <c r="E99">
-        <v>-45.23140805078584</v>
+        <v>-43.92262698511801</v>
       </c>
       <c r="F99">
-        <v>-6.185775408261451</v>
+        <v>-6.718611679805138</v>
       </c>
       <c r="G99">
-        <v>-5.905812449450236</v>
+        <v>-6.277020610223175</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.523372939117838</v>
       </c>
       <c r="E100">
-        <v>-46.81974087389516</v>
+        <v>-45.51726117980902</v>
       </c>
       <c r="F100">
-        <v>-5.85179321072513</v>
+        <v>-6.224733386001825</v>
       </c>
       <c r="G100">
-        <v>-6.612210035528843</v>
+        <v>-6.607919568509948</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.454165695907292</v>
       </c>
       <c r="E101">
-        <v>-50.02536837562988</v>
+        <v>-49.43494027391731</v>
       </c>
       <c r="F101">
-        <v>-5.715196991812562</v>
+        <v>-6.431361476421603</v>
       </c>
       <c r="G101">
-        <v>-7.274954768126621</v>
+        <v>-6.75063056561685</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.419596562773945</v>
       </c>
       <c r="E102">
-        <v>-52.27349646530127</v>
+        <v>-51.16014848814547</v>
       </c>
       <c r="F102">
-        <v>-5.340812080814508</v>
+        <v>-6.51281305535857</v>
       </c>
       <c r="G102">
-        <v>-7.43121582812576</v>
+        <v>-6.692040530662829</v>
       </c>
     </row>
   </sheetData>
